--- a/tien_dien.xlsx
+++ b/tien_dien.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="11460" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="20">
   <si>
     <t>THÔNG TIN TIỀN ĐIỆN HÀNG THÁNG</t>
   </si>
@@ -3839,10 +3839,34 @@
         <f>((D4-C4)*F4)+G4</f>
         <v>482400</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="I4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="20.25" spans="1:9">
       <c r="A5" s="4"/>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4683</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4850</v>
+      </c>
+      <c r="E5" s="5">
+        <f>D5-C5</f>
+        <v>167</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3600</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
+        <f>((D5-C5)*F5)+G5</f>
+        <v>601200</v>
+      </c>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="4"/>
@@ -3953,10 +3977,33 @@
         <f>((D20-C20)*F20)+G20</f>
         <v>554400</v>
       </c>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:1">
+      <c r="I20" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="18.75" spans="1:8">
       <c r="A21" s="4"/>
+      <c r="B21" s="5">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3859</v>
+      </c>
+      <c r="D21" s="5">
+        <v>3987</v>
+      </c>
+      <c r="E21" s="5">
+        <f>D21-C21</f>
+        <v>128</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3600</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5">
+        <f>((D21-C21)*F21)+G21</f>
+        <v>460800</v>
+      </c>
     </row>
     <row r="22" customFormat="1" spans="1:1">
       <c r="A22" s="4"/>
@@ -4064,10 +4111,33 @@
         <f>((D36-C36)*F36)+G36</f>
         <v>658800</v>
       </c>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" customFormat="1" spans="1:1">
+      <c r="I36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="18.75" spans="1:8">
       <c r="A37" s="4"/>
+      <c r="B37" s="5">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>4306</v>
+      </c>
+      <c r="D37" s="5">
+        <v>4486</v>
+      </c>
+      <c r="E37" s="5">
+        <f>D37-C37</f>
+        <v>180</v>
+      </c>
+      <c r="F37" s="5">
+        <v>3600</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5">
+        <f>((D37-C37)*F37)+G37</f>
+        <v>648000</v>
+      </c>
     </row>
     <row r="38" customFormat="1" spans="1:1">
       <c r="A38" s="4"/>

--- a/tien_dien.xlsx
+++ b/tien_dien.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11460" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="20">
   <si>
     <t>THÔNG TIN TIỀN ĐIỆN HÀNG THÁNG</t>
   </si>
@@ -87,7 +87,7 @@
     <t>NHÀ SỐ 3</t>
   </si>
   <si>
-    <t>Anh Vũ</t>
+    <t>Chị Phĩ</t>
   </si>
 </sst>
 </file>
@@ -800,7 +800,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1159,7 +1159,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" ht="18.75" spans="1:10">
+    <row r="3" ht="18.75" spans="1:15">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="20.25" spans="1:9">
+    <row r="4" ht="20.25" spans="1:15">
       <c r="A4" s="4">
         <v>2023</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="20.25" spans="1:9">
+    <row r="5" ht="20.25" spans="1:15">
       <c r="A5" s="4"/>
       <c r="B5" s="5">
         <v>11</v>
@@ -1251,7 +1251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" ht="20.25" spans="1:9">
+    <row r="6" ht="20.25" spans="1:15">
       <c r="A6" s="4"/>
       <c r="B6" s="5">
         <v>12</v>
@@ -1280,15 +1280,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:15">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:15">
       <c r="A8" s="4">
         <v>2024</v>
       </c>
     </row>
-    <row r="9" ht="20.25" spans="1:9">
+    <row r="9" ht="20.25" spans="1:15">
       <c r="A9" s="4"/>
       <c r="B9" s="5">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="20.25" spans="1:9">
+    <row r="10" ht="20.25" spans="1:15">
       <c r="A10" s="4"/>
       <c r="B10" s="5">
         <v>2</v>
@@ -1346,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="20.25" spans="1:9">
+    <row r="11" ht="20.25" spans="1:15">
       <c r="A11" s="4"/>
       <c r="B11" s="5">
         <v>3</v>
@@ -1375,7 +1375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="20.25" spans="1:9">
+    <row r="12" ht="20.25" spans="1:15">
       <c r="A12" s="4"/>
       <c r="B12" s="5">
         <v>4</v>
@@ -1404,7 +1404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" ht="20.25" spans="1:9">
+    <row r="13" ht="20.25" spans="1:15">
       <c r="A13" s="4"/>
       <c r="B13" s="5">
         <v>5</v>
@@ -1433,7 +1433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" ht="20.25" spans="1:9">
+    <row r="14" ht="20.25" spans="1:15">
       <c r="A14" s="4"/>
       <c r="B14" s="5">
         <v>6</v>
@@ -1462,7 +1462,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="20.25" spans="1:9">
+    <row r="15" ht="20.25" spans="1:15">
       <c r="A15" s="4"/>
       <c r="B15" s="5">
         <v>7</v>
@@ -1491,7 +1491,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" ht="20.25" spans="1:9">
+    <row r="16" ht="20.25" spans="1:15">
       <c r="A16" s="4"/>
       <c r="B16" s="5">
         <v>8</v>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" ht="20.25" spans="1:9">
+    <row r="17" ht="20.25" spans="1:10">
       <c r="A17" s="4"/>
       <c r="B17" s="5">
         <v>9</v>
@@ -1549,7 +1549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="20.25" spans="1:9">
+    <row r="18" ht="20.25" spans="1:10">
       <c r="A18" s="4"/>
       <c r="B18" s="5">
         <v>10</v>
@@ -1578,7 +1578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" ht="20.25" spans="2:9">
+    <row r="19" ht="20.25" spans="1:10">
       <c r="B19" s="5">
         <v>11</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="20.25" spans="2:9">
+    <row r="20" customFormat="1" ht="20.25" spans="1:10">
       <c r="B20" s="5">
         <v>12</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" ht="21" spans="1:1">
+    <row r="21" s="7" customFormat="1" ht="21" spans="1:10">
       <c r="A21" s="7" t="s">
         <v>14</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="20.25" spans="1:9">
+    <row r="23" customFormat="1" ht="20.25" spans="1:10">
       <c r="A23" s="4">
         <v>2025</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" customFormat="1" ht="20.25" spans="1:9">
+    <row r="24" customFormat="1" ht="20.25" spans="1:10">
       <c r="A24" s="4"/>
       <c r="B24" s="5">
         <v>2</v>
@@ -1727,7 +1727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="20.25" spans="1:9">
+    <row r="25" customFormat="1" ht="20.25" spans="1:10">
       <c r="A25" s="4"/>
       <c r="B25" s="5">
         <v>3</v>
@@ -1754,7 +1754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" customFormat="1" ht="20.25" spans="1:9">
+    <row r="26" customFormat="1" ht="20.25" spans="1:10">
       <c r="A26" s="4"/>
       <c r="B26" s="5">
         <v>4</v>
@@ -1781,7 +1781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" ht="20.25" spans="2:9">
+    <row r="27" ht="20.25" spans="1:10">
       <c r="B27" s="5">
         <v>5</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" ht="20.25" spans="2:9">
+    <row r="28" ht="20.25" spans="1:10">
       <c r="B28" s="5">
         <v>6</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" ht="20.25" spans="2:9">
+    <row r="29" ht="20.25" spans="1:10">
       <c r="B29" s="5">
         <v>7</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" ht="20.25" spans="2:9">
+    <row r="30" ht="20.25" spans="1:10">
       <c r="B30" s="5">
         <v>8</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" customFormat="1" ht="20.25" spans="2:9">
+    <row r="31" customFormat="1" ht="20.25" spans="1:10">
       <c r="B31" s="5">
         <v>9</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" ht="20.25" spans="2:9">
+    <row r="32" ht="20.25" spans="1:10">
       <c r="B32" s="5">
         <v>10</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" ht="20.25" spans="2:9">
+    <row r="33" ht="20.25" spans="1:10">
       <c r="B33" s="5">
         <v>11</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" ht="20.25" spans="2:9">
+    <row r="34" ht="20.25" spans="1:10">
       <c r="B34" s="5">
         <v>12</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" s="7" customFormat="1" ht="21" spans="1:1">
+    <row r="36" s="7" customFormat="1" ht="21" spans="1:10">
       <c r="A36" s="7" t="s">
         <v>14</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="20.25" spans="1:9">
+    <row r="38" customFormat="1" ht="20.25" spans="1:10">
       <c r="A38" s="4">
         <v>2026</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="20.25" spans="1:9">
+    <row r="39" customFormat="1" ht="20.25" spans="1:10">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2066,7 +2066,7 @@
       <c r="H39" s="5"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" customFormat="1" ht="20.25" spans="1:9">
+    <row r="40" customFormat="1" ht="20.25" spans="1:10">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2077,7 +2077,7 @@
       <c r="H40" s="5"/>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" customFormat="1" ht="20.25" spans="1:9">
+    <row r="41" customFormat="1" ht="20.25" spans="1:10">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2088,19 +2088,19 @@
       <c r="H41" s="5"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" ht="18.75" spans="1:1">
+    <row r="42" ht="18.75" spans="1:10">
       <c r="A42" s="4"/>
     </row>
-    <row r="43" ht="18.75" spans="1:1">
+    <row r="43" ht="18.75" spans="1:10">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" ht="18.75" spans="1:1">
+    <row r="44" ht="18.75" spans="1:10">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" ht="18.75" spans="1:1">
+    <row r="45" ht="18.75" spans="1:10">
       <c r="A45" s="4"/>
     </row>
-    <row r="51" ht="21" spans="2:15">
+    <row r="51" ht="21" spans="1:15">
       <c r="B51" s="2"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -2116,7 +2116,7 @@
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" ht="21" spans="2:15">
+    <row r="52" ht="21" spans="1:15">
       <c r="B52" s="2"/>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -2134,7 +2134,7 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
     </row>
-    <row r="53" ht="18.75" spans="2:10">
+    <row r="53" ht="18.75" spans="1:15">
       <c r="B53" s="4" t="s">
         <v>4</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" ht="20.25" spans="2:9">
+    <row r="54" ht="20.25" spans="1:15">
       <c r="B54" s="5">
         <v>10</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" ht="21" spans="1:9">
+    <row r="55" ht="21" spans="1:15">
       <c r="A55" s="2"/>
       <c r="B55" s="5">
         <v>11</v>
@@ -2220,22 +2220,22 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" ht="21" spans="1:1">
+    <row r="56" ht="21" spans="1:15">
       <c r="A56" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" ht="18.75" spans="1:1">
+    <row r="57" ht="18.75" spans="1:15">
       <c r="A57" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:15">
       <c r="A58" s="4">
         <v>2023</v>
       </c>
     </row>
-    <row r="59" ht="20.25" spans="1:9">
+    <row r="59" ht="20.25" spans="1:15">
       <c r="A59" s="4"/>
       <c r="B59" s="5">
         <v>4</v>
@@ -2264,7 +2264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" ht="20.25" spans="1:9">
+    <row r="60" ht="20.25" spans="1:15">
       <c r="A60" s="4"/>
       <c r="B60" s="5">
         <v>5</v>
@@ -2293,7 +2293,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" ht="20.25" spans="1:9">
+    <row r="61" ht="20.25" spans="1:15">
       <c r="A61" s="4"/>
       <c r="B61" s="5">
         <v>6</v>
@@ -2322,7 +2322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" ht="20.25" spans="1:9">
+    <row r="62" ht="20.25" spans="1:15">
       <c r="A62" s="4">
         <v>2024</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" ht="20.25" spans="1:9">
+    <row r="63" ht="20.25" spans="1:15">
       <c r="A63" s="4"/>
       <c r="B63" s="5">
         <v>8</v>
@@ -2382,7 +2382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" ht="20.25" spans="1:9">
+    <row r="64" ht="20.25" spans="1:15">
       <c r="A64" s="4"/>
       <c r="B64" s="5">
         <v>9</v>
@@ -2411,7 +2411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" customFormat="1" ht="20.25" spans="1:9">
+    <row r="65" customFormat="1" ht="20.25" spans="1:10">
       <c r="A65" s="4"/>
       <c r="B65" s="5">
         <v>10</v>
@@ -2440,7 +2440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" ht="20.25" spans="2:9">
+    <row r="66" ht="20.25" spans="1:10">
       <c r="B66" s="5">
         <v>11</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" customFormat="1" ht="20.25" spans="2:9">
+    <row r="67" customFormat="1" ht="20.25" spans="1:10">
       <c r="B67" s="5">
         <v>12</v>
       </c>
@@ -2496,13 +2496,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" s="8" customFormat="1" ht="21" spans="1:5">
+    <row r="68" s="8" customFormat="1" ht="21" spans="1:10">
       <c r="A68"/>
       <c r="E68" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="69" ht="18.75" spans="2:10">
+    <row r="69" ht="18.75" spans="1:10">
       <c r="B69" s="4" t="s">
         <v>4</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" customFormat="1" ht="20.25" spans="2:9">
+    <row r="70" customFormat="1" ht="20.25" spans="1:10">
       <c r="B70" s="5">
         <v>1</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" customFormat="1" ht="20.25" spans="2:9">
+    <row r="71" customFormat="1" ht="20.25" spans="1:10">
       <c r="B71" s="5">
         <v>2</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" customFormat="1" ht="20.25" spans="1:9">
+    <row r="72" customFormat="1" ht="20.25" spans="1:10">
       <c r="A72" s="8"/>
       <c r="B72" s="5">
         <v>3</v>
@@ -2610,7 +2610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" customFormat="1" ht="20.25" spans="1:9">
+    <row r="73" customFormat="1" ht="20.25" spans="1:10">
       <c r="A73" s="4" t="s">
         <v>3</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" ht="20.25" spans="1:9">
+    <row r="74" ht="20.25" spans="1:10">
       <c r="A74" s="4">
         <v>2025</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" ht="20.25" spans="1:9">
+    <row r="75" ht="20.25" spans="1:10">
       <c r="A75" s="4"/>
       <c r="B75" s="5">
         <v>6</v>
@@ -2695,7 +2695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" ht="20.25" spans="1:9">
+    <row r="76" ht="20.25" spans="1:10">
       <c r="A76" s="4"/>
       <c r="B76" s="5">
         <v>7</v>
@@ -2722,7 +2722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" ht="20.25" spans="1:9">
+    <row r="77" ht="20.25" spans="1:10">
       <c r="A77" s="4"/>
       <c r="B77" s="5">
         <v>8</v>
@@ -2749,7 +2749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" customFormat="1" ht="20.25" spans="2:9">
+    <row r="78" customFormat="1" ht="20.25" spans="1:10">
       <c r="B78" s="5">
         <v>9</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" ht="20.25" spans="2:9">
+    <row r="79" ht="20.25" spans="1:10">
       <c r="B79" s="5">
         <v>10</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" ht="20.25" spans="2:9">
+    <row r="80" ht="20.25" spans="1:10">
       <c r="B80" s="5">
         <v>11</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" ht="18.75" spans="2:8">
+    <row r="81" ht="18.75" spans="1:15">
       <c r="B81" s="5">
         <v>12</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>647500</v>
       </c>
     </row>
-    <row r="82" ht="18.75" spans="2:8">
+    <row r="82" ht="18.75" spans="1:15">
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
@@ -2859,7 +2859,7 @@
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
     </row>
-    <row r="84" ht="21" spans="2:15">
+    <row r="84" ht="21" spans="1:15">
       <c r="B84" s="2"/>
       <c r="C84" s="3" t="s">
         <v>17</v>
@@ -2877,7 +2877,7 @@
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
     </row>
-    <row r="85" ht="18.75" spans="2:10">
+    <row r="85" ht="18.75" spans="1:15">
       <c r="B85" s="4" t="s">
         <v>4</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" ht="20.25" spans="2:9">
+    <row r="86" ht="20.25" spans="1:15">
       <c r="B86" s="5">
         <v>10</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" ht="20.25" spans="2:9">
+    <row r="87" ht="20.25" spans="1:15">
       <c r="B87" s="5">
         <v>11</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" ht="21" spans="1:9">
+    <row r="88" ht="21" spans="1:15">
       <c r="A88" s="2" t="s">
         <v>18</v>
       </c>
@@ -2993,12 +2993,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" ht="18.75" spans="1:1">
+    <row r="89" ht="18.75" spans="1:15">
       <c r="A89" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" ht="20.25" spans="1:9">
+    <row r="90" ht="20.25" spans="1:15">
       <c r="A90" s="4">
         <v>2023</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" ht="20.25" spans="1:9">
+    <row r="91" ht="20.25" spans="1:15">
       <c r="A91" s="4"/>
       <c r="B91" s="5">
         <v>2</v>
@@ -3058,7 +3058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" ht="20.25" spans="1:9">
+    <row r="92" ht="20.25" spans="1:15">
       <c r="A92" s="4"/>
       <c r="B92" s="5">
         <v>3</v>
@@ -3087,7 +3087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" ht="20.25" spans="1:9">
+    <row r="93" ht="20.25" spans="1:15">
       <c r="A93" s="4"/>
       <c r="B93" s="5">
         <v>4</v>
@@ -3116,7 +3116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" ht="20.25" spans="1:9">
+    <row r="94" ht="20.25" spans="1:15">
       <c r="A94" s="4">
         <v>2024</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" ht="20.25" spans="1:9">
+    <row r="95" ht="20.25" spans="1:15">
       <c r="A95" s="4"/>
       <c r="B95" s="5">
         <v>6</v>
@@ -3176,7 +3176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" ht="20.25" spans="1:9">
+    <row r="96" ht="20.25" spans="1:15">
       <c r="A96" s="4"/>
       <c r="B96" s="5">
         <v>7</v>
@@ -3205,7 +3205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" ht="20.25" spans="1:9">
+    <row r="97" ht="20.25" spans="1:10">
       <c r="A97" s="4"/>
       <c r="B97" s="5">
         <v>8</v>
@@ -3234,7 +3234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" ht="20.25" spans="2:9">
+    <row r="98" ht="20.25" spans="1:10">
       <c r="B98" s="5">
         <v>9</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" customFormat="1" ht="20.25" spans="2:9">
+    <row r="99" customFormat="1" ht="20.25" spans="1:10">
       <c r="B99" s="5">
         <v>10</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" ht="20.25" spans="2:9">
+    <row r="100" ht="20.25" spans="1:10">
       <c r="B100" s="5">
         <v>11</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" customFormat="1" ht="20.25" spans="2:9">
+    <row r="101" customFormat="1" ht="20.25" spans="1:10">
       <c r="B101" s="5">
         <v>12</v>
       </c>
@@ -3346,13 +3346,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" s="8" customFormat="1" ht="21" spans="1:5">
+    <row r="102" s="8" customFormat="1" ht="21" spans="1:10">
       <c r="A102"/>
       <c r="E102" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="103" ht="18.75" spans="2:10">
+    <row r="103" ht="18.75" spans="1:10">
       <c r="B103" s="4" t="s">
         <v>4</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" customFormat="1" ht="20.25" spans="2:9">
+    <row r="104" customFormat="1" ht="20.25" spans="1:10">
       <c r="B104" s="5">
         <v>1</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" customFormat="1" ht="20.25" spans="2:9">
+    <row r="105" customFormat="1" ht="20.25" spans="1:10">
       <c r="B105" s="5">
         <v>2</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" customFormat="1" ht="20.25" spans="1:9">
+    <row r="106" customFormat="1" ht="20.25" spans="1:10">
       <c r="A106" s="8"/>
       <c r="B106" s="5">
         <v>3</v>
@@ -3460,7 +3460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" customFormat="1" ht="20.25" spans="1:9">
+    <row r="107" customFormat="1" ht="20.25" spans="1:10">
       <c r="A107" s="4" t="s">
         <v>3</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" ht="20.25" spans="1:9">
+    <row r="108" ht="20.25" spans="1:10">
       <c r="A108" s="4">
         <v>2025</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" ht="20.25" spans="1:9">
+    <row r="109" ht="20.25" spans="1:10">
       <c r="A109" s="4"/>
       <c r="B109" s="5">
         <v>6</v>
@@ -3545,7 +3545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" ht="20.25" spans="1:9">
+    <row r="110" ht="20.25" spans="1:10">
       <c r="A110" s="4"/>
       <c r="B110" s="5">
         <v>7</v>
@@ -3572,7 +3572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" ht="20.25" spans="1:9">
+    <row r="111" ht="20.25" spans="1:10">
       <c r="A111" s="4"/>
       <c r="B111" s="5">
         <v>8</v>
@@ -3599,7 +3599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" customFormat="1" ht="20.25" spans="2:9">
+    <row r="112" customFormat="1" ht="20.25" spans="1:10">
       <c r="B112" s="5">
         <v>9</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" ht="18.75" spans="2:8">
+    <row r="115" ht="18.75" spans="2:9">
       <c r="B115" s="5">
         <v>12</v>
       </c>
@@ -3784,7 +3784,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" ht="18.75" spans="1:10">
+    <row r="3" ht="18.75" spans="1:15">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>4</v>
@@ -3814,7 +3814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="20.25" spans="1:9">
+    <row r="4" ht="20.25" spans="1:15">
       <c r="A4" s="4">
         <v>2026</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>4683</v>
       </c>
       <c r="E4" s="5">
-        <f>D4-C4</f>
+        <f t="shared" ref="E4:E7" si="0">D4-C4</f>
         <v>134</v>
       </c>
       <c r="F4" s="5">
@@ -3836,14 +3836,14 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
-        <f>((D4-C4)*F4)+G4</f>
+        <f t="shared" ref="H4:H7" si="1">((D4-C4)*F4)+G4</f>
         <v>482400</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="20.25" spans="1:9">
+    <row r="5" ht="20.25" spans="1:15">
       <c r="A5" s="4"/>
       <c r="B5" s="5">
         <v>2</v>
@@ -3855,7 +3855,7 @@
         <v>4850</v>
       </c>
       <c r="E5" s="5">
-        <f>D5-C5</f>
+        <f t="shared" si="0"/>
         <v>167</v>
       </c>
       <c r="F5" s="5">
@@ -3863,42 +3863,89 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
-        <f>((D5-C5)*F5)+G5</f>
+        <f t="shared" si="1"/>
         <v>601200</v>
       </c>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="I5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="20.25" spans="1:15">
       <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4850</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5059</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>209</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3500</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>731500</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" spans="1:15">
       <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5059</v>
+      </c>
+      <c r="D7" s="5">
+        <v>5287</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>228</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3300</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
+        <f t="shared" si="1"/>
+        <v>752400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:15">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:15">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:15">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:15">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:15">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:15">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:15">
       <c r="A15" s="4"/>
     </row>
-    <row r="17" ht="18.75" spans="1:1">
+    <row r="17" ht="18.75" spans="1:15">
       <c r="A17" s="4"/>
     </row>
     <row r="18" ht="21" spans="1:15">
@@ -3922,7 +3969,7 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" ht="18.75" spans="1:10">
+    <row r="19" ht="18.75" spans="1:15">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>4</v>
@@ -3952,7 +3999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="20.25" spans="1:9">
+    <row r="20" customFormat="1" ht="20.25" spans="1:15">
       <c r="A20" s="4">
         <v>2026</v>
       </c>
@@ -3966,7 +4013,7 @@
         <v>3859</v>
       </c>
       <c r="E20" s="5">
-        <f>D20-C20</f>
+        <f t="shared" ref="E20:E23" si="2">D20-C20</f>
         <v>154</v>
       </c>
       <c r="F20" s="5">
@@ -3974,14 +4021,14 @@
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
-        <f>((D20-C20)*F20)+G20</f>
+        <f t="shared" ref="H20:H23" si="3">((D20-C20)*F20)+G20</f>
         <v>554400</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" customFormat="1" ht="18.75" spans="1:8">
+    <row r="21" customFormat="1" ht="20.25" spans="1:15">
       <c r="A21" s="4"/>
       <c r="B21" s="5">
         <v>2</v>
@@ -3993,7 +4040,7 @@
         <v>3987</v>
       </c>
       <c r="E21" s="5">
-        <f>D21-C21</f>
+        <f t="shared" si="2"/>
         <v>128</v>
       </c>
       <c r="F21" s="5">
@@ -4001,38 +4048,86 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
-        <f>((D21-C21)*F21)+G21</f>
+        <f t="shared" si="3"/>
         <v>460800</v>
       </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:1">
+      <c r="I21" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="20.25" spans="1:15">
       <c r="A22" s="4"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:1">
+      <c r="B22" s="5">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3987</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4179</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="F22" s="5">
+        <v>3500</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <f t="shared" si="3"/>
+        <v>672000</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="18.75" spans="1:15">
       <c r="A23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:1">
+      <c r="B23" s="5">
+        <v>4</v>
+      </c>
+      <c r="C23" s="5">
+        <v>4179</v>
+      </c>
+      <c r="D23" s="5">
+        <v>4429</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3300</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5">
+        <f t="shared" si="3"/>
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:15">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" customFormat="1" spans="1:1">
+    <row r="25" customFormat="1" spans="1:15">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" customFormat="1" spans="1:1">
+    <row r="26" customFormat="1" spans="1:15">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" customFormat="1" spans="1:1">
+    <row r="27" customFormat="1" spans="1:15">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" customFormat="1" spans="1:1">
+    <row r="28" customFormat="1" spans="1:15">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" customFormat="1" spans="1:1">
+    <row r="29" customFormat="1" spans="1:15">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" customFormat="1" spans="1:1">
+    <row r="30" customFormat="1" spans="1:15">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" customFormat="1" spans="1:1">
+    <row r="31" customFormat="1" spans="1:15">
       <c r="A31" s="4"/>
     </row>
     <row r="34" ht="21" spans="1:15">
@@ -4056,7 +4151,7 @@
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" ht="18.75" spans="1:10">
+    <row r="35" ht="18.75" spans="1:15">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>4</v>
@@ -4086,7 +4181,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="20.25" spans="1:9">
+    <row r="36" customFormat="1" ht="20.25" spans="1:15">
       <c r="A36" s="4">
         <v>2026</v>
       </c>
@@ -4100,7 +4195,7 @@
         <v>4306</v>
       </c>
       <c r="E36" s="5">
-        <f>D36-C36</f>
+        <f t="shared" ref="E36:E39" si="4">D36-C36</f>
         <v>183</v>
       </c>
       <c r="F36" s="5">
@@ -4108,14 +4203,14 @@
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
-        <f>((D36-C36)*F36)+G36</f>
+        <f t="shared" ref="H36:H39" si="5">((D36-C36)*F36)+G36</f>
         <v>658800</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="18.75" spans="1:8">
+    <row r="37" customFormat="1" ht="20.25" spans="1:15">
       <c r="A37" s="4"/>
       <c r="B37" s="5">
         <v>2</v>
@@ -4127,7 +4222,7 @@
         <v>4486</v>
       </c>
       <c r="E37" s="5">
-        <f>D37-C37</f>
+        <f t="shared" si="4"/>
         <v>180</v>
       </c>
       <c r="F37" s="5">
@@ -4135,38 +4230,86 @@
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
-        <f>((D37-C37)*F37)+G37</f>
+        <f t="shared" si="5"/>
         <v>648000</v>
       </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:1">
+      <c r="I37" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="20.25" spans="1:15">
       <c r="A38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" spans="1:1">
+      <c r="B38" s="5">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5">
+        <v>4486</v>
+      </c>
+      <c r="D38" s="5">
+        <v>4620</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="4"/>
+        <v>134</v>
+      </c>
+      <c r="F38" s="5">
+        <v>3500</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5">
+        <f t="shared" si="5"/>
+        <v>469000</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="18.75" spans="1:15">
       <c r="A39" s="4"/>
-    </row>
-    <row r="40" customFormat="1" spans="1:1">
+      <c r="B39" s="5">
+        <v>4</v>
+      </c>
+      <c r="C39" s="5">
+        <v>4620</v>
+      </c>
+      <c r="D39" s="5">
+        <v>4737</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="4"/>
+        <v>117</v>
+      </c>
+      <c r="F39" s="5">
+        <v>3300</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5">
+        <f t="shared" si="5"/>
+        <v>386100</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:15">
       <c r="A40" s="4"/>
     </row>
-    <row r="41" customFormat="1" spans="1:1">
+    <row r="41" customFormat="1" spans="1:15">
       <c r="A41" s="4"/>
     </row>
-    <row r="42" customFormat="1" spans="1:1">
+    <row r="42" customFormat="1" spans="1:15">
       <c r="A42" s="4"/>
     </row>
-    <row r="43" customFormat="1" spans="1:1">
+    <row r="43" customFormat="1" spans="1:15">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" customFormat="1" spans="1:1">
+    <row r="44" customFormat="1" spans="1:15">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" customFormat="1" spans="1:1">
+    <row r="45" customFormat="1" spans="1:15">
       <c r="A45" s="4"/>
     </row>
-    <row r="46" customFormat="1" spans="1:1">
+    <row r="46" customFormat="1" spans="1:15">
       <c r="A46" s="4"/>
     </row>
-    <row r="47" customFormat="1" spans="1:1">
+    <row r="47" customFormat="1" spans="1:15">
       <c r="A47" s="4"/>
     </row>
   </sheetData>
